--- a/ig/update-vs-url/ValueSet-fr-core-contact-relationship.xlsx
+++ b/ig/update-vs-url/ValueSet-fr-core-contact-relationship.xlsx
@@ -8,7 +8,7 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from 0131" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from FR Core CodeSyst" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from fr-core-contact-" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-30T11:02:30+00:00</t>
+    <t>2023-11-06T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -607,7 +607,7 @@
     <t>neighbor</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/CodeSystem/fr-core-contact-relationship</t>
+    <t>https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-contact-relationship</t>
   </si>
 </sst>
 </file>

--- a/ig/update-vs-url/ValueSet-fr-core-contact-relationship.xlsx
+++ b/ig/update-vs-url/ValueSet-fr-core-contact-relationship.xlsx
@@ -8,7 +8,7 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from 0131" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from fr-core-contact-" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from FR Core CodeSyst" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-contact-relationship</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-contact-relationship</t>
   </si>
   <si>
     <t>Version</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:17:56+00:00</t>
+    <t>2023-11-07T10:08:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/ValueSet-fr-core-contact-relationship.xlsx
+++ b/ig/update-vs-url/ValueSet-fr-core-contact-relationship.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:08:49+00:00</t>
+    <t>2023-11-07T10:16:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/ValueSet-fr-core-contact-relationship.xlsx
+++ b/ig/update-vs-url/ValueSet-fr-core-contact-relationship.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:16:09+00:00</t>
+    <t>2023-11-07T10:18:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/ValueSet-fr-core-contact-relationship.xlsx
+++ b/ig/update-vs-url/ValueSet-fr-core-contact-relationship.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:18:25+00:00</t>
+    <t>2023-11-07T10:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/ValueSet-fr-core-contact-relationship.xlsx
+++ b/ig/update-vs-url/ValueSet-fr-core-contact-relationship.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:25:25+00:00</t>
+    <t>2023-11-07T10:39:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/ValueSet-fr-core-contact-relationship.xlsx
+++ b/ig/update-vs-url/ValueSet-fr-core-contact-relationship.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:39:28+00:00</t>
+    <t>2023-11-07T10:47:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/update-vs-url/ValueSet-fr-core-contact-relationship.xlsx
+++ b/ig/update-vs-url/ValueSet-fr-core-contact-relationship.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T10:47:16+00:00</t>
+    <t>2023-11-07T10:49:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
